--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は34系統・139件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
+          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は35系統・143件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
         </is>
       </c>
     </row>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1229</v>
+        <v>1238</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>26</v>
@@ -683,12 +683,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>+703</t>
+          <t>+712</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>+116</t>
+          <t>+117</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>系統ごとの件数（34系統・139件）</t>
+          <t>系統ごとの件数（35系統・143件）</t>
         </is>
       </c>
     </row>
@@ -1731,72 +1731,102 @@
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>追記</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_houkoku_hanei.py</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>レビュー反映版の第6章と前期計画の具体的な取組み38件を正本と突き合わせ、落ちていた4件を足した</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n">
+      <c r="B47" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>図の作成</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>build_kitashiobara_graph.py</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>他メンバー版の図は画像で取り込まれており数値を直せないため、当方で作り直せる図を別に作った</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>34系統</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>※ 型ごとの内訳は 追記 104件／移植 20件／図の作成 10件／書き換え 5件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>35系統</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>※ 型ごとの内訳は 追記 108件／移植 20件／図の作成 10件／書き換え 5件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
+        </is>
+      </c>
+    </row>
     <row r="51"/>
     <row r="52"/>
     <row r="53"/>
+    <row r="54"/>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A50:F54"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A49:F53"/>
     <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1809,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1824,7 +1854,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全139件</t>
+          <t>全143件</t>
         </is>
       </c>
     </row>
@@ -6648,22 +6678,22 @@
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Z-1</t>
+          <t>ＳＲ-1</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C135" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>第5章2（1）住民への情報提供等</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -6673,34 +6703,34 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文2・注記1</t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>第4次北塩原村障がい者計画（通し頁26。本文頁22）６生活環境（２）③防災ネットワークの確立／アンケート調査結果報告書（令和８年10月22日版）第６章課題６</t>
         </is>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>Z-2</t>
+          <t>ＳＲ-2</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>第5章3（2）理解促進研修・啓発事業</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -6710,34 +6740,34 @@
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文1</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>第4次北塩原村障がい者計画（通し頁26。本文頁22）４教育・育成（１）④福祉教育の推進／アンケート調査結果報告書（令和８年10月22日版）第６章課題６</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Z-3</t>
+          <t>ＳＲ-3</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C137" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>第5章3（2）移動支援事業</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
@@ -6747,34 +6777,34 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文1</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（各年４月１日現在）</t>
+          <t>アンケート調査結果報告書（令和８年10月22日版）第６章課題２</t>
         </is>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>Z-4</t>
+          <t>ＳＲ-4</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C138" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
+          <t>第3章3 基本施策の目標値と本計画期間の主な取組み</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -6784,19 +6814,19 @@
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文1</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+          <t>アンケート調査結果報告書（令和８年10月22日版）第６章課題３</t>
         </is>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Z-5</t>
+          <t>Z-1</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -6811,12 +6841,12 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
+          <t>（１）給付費の推移</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -6826,14 +6856,14 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章６により作成）</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Z-6</t>
+          <t>Z-2</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
@@ -6848,12 +6878,12 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+          <t>（３）サービス別の構成（令和７年度）</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -6863,14 +6893,14 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Z-7</t>
+          <t>Z-3</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -6885,12 +6915,12 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+          <t>（１）高齢化率</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -6900,14 +6930,14 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章２（11）により作成）</t>
+          <t>資料：北塩原村（各年４月１日現在）</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>Z-4</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
@@ -6922,7 +6952,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -6937,14 +6967,14 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Z-9</t>
+          <t>Z-5</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -6959,7 +6989,7 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
@@ -6974,42 +7004,190 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+          <t>資料：北塩原村（第５章６により作成）</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
+          <t>Z-6</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>Z-7</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章２（11）により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>Z-10</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>Z-9</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
           <t>Z-8</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
-      <c r="C144" s="19" t="inlineStr">
+      <c r="C148" s="19" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なります。</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E148" s="6" t="inlineStr">
         <is>
           <t>表の後</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <t>図1点</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr">
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>資料：障害者総合支援法第７条及び本計画により作成</t>
         </is>
@@ -7030,7 +7208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7043,7 +7221,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>生成器が実際に開いているエビデンス 38点</t>
+          <t>生成器が実際に開いているエビデンス 40点</t>
         </is>
       </c>
     </row>
@@ -7089,22 +7267,22 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>報告書用集計表.xlsx</t>
+          <t>アンケート調査結果報告書_令和8年10月21日版.docx</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>282KB</t>
+          <t>4,465KB</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>942段落</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>アンケート集計表の改訂版</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
         </is>
       </c>
     </row>
@@ -7116,76 +7294,76 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>集計_障がい者版.xlsx</t>
+          <t>アンケート調査結果報告書_令和8年10月22日版_レビュー反映.docx</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>150KB</t>
+          <t>4,478KB</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>945段落</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>指標の測定可能性</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>レビュー_20261010</t>
+          <t>アンケート結果</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_MECEレビュー_利用の流れと報酬改定_20261010.md</t>
+          <t>報告書用集計表.xlsx</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18KB</t>
+          <t>282KB</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>503行</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（制度）／ＭＥＣＥ（利用の流れと報酬改定）</t>
+          <t>アンケート集計表の改訂版</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>レビュー_20261010</t>
+          <t>アンケート結果</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_RedTeamレビュー_広域連携圏域整合_20261010.md</t>
+          <t>集計_障がい者版.xlsx</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>39KB</t>
+          <t>150KB</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>1079行</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
+          <t>指標の測定可能性</t>
         </is>
       </c>
     </row>
@@ -7197,22 +7375,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_RedTeamレビュー_救急防災冬季_20261010.md</t>
+          <t>北塩原村_MECEレビュー_利用の流れと報酬改定_20261010.md</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>14KB</t>
+          <t>18KB</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>455行</t>
+          <t>503行</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>事実の誤りの書き換え（制度）／ＭＥＣＥ（利用の流れと報酬改定）</t>
         </is>
       </c>
     </row>
@@ -7224,22 +7402,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_アンケートと見込量の整合RedTeam_20261010.md</t>
+          <t>北塩原村_RedTeamレビュー_広域連携圏域整合_20261010.md</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>15KB</t>
+          <t>39KB</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>666行</t>
+          <t>1079行</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合</t>
+          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
         </is>
       </c>
     </row>
@@ -7251,22 +7429,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_共生型サービスの適用可能性レビュー_20261011.md</t>
+          <t>北塩原村_RedTeamレビュー_救急防災冬季_20261010.md</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>28KB</t>
+          <t>14KB</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>876行</t>
+          <t>455行</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>共生型サービスの適用可能性</t>
+          <t>ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -7278,22 +7456,22 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_国予算R7R8_MECE_RedTeamレビュー_20261010.md</t>
+          <t>北塩原村_アンケートと見込量の整合RedTeam_20261010.md</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>37KB</t>
+          <t>15KB</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1190行</t>
+          <t>666行</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>アンケートと見込量の整合</t>
         </is>
       </c>
     </row>
@@ -7305,22 +7483,22 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_国予算レビュー反証確認_訂正版_20261011.md</t>
+          <t>北塩原村_共生型サービスの適用可能性レビュー_20261011.md</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20KB</t>
+          <t>28KB</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>666行</t>
+          <t>876行</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>共生型サービスの適用可能性</t>
         </is>
       </c>
     </row>
@@ -7332,22 +7510,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_情報公表制度と経営情報見える化の計画反映レビュー_20261010.md</t>
+          <t>北塩原村_国予算R7R8_MECE_RedTeamレビュー_20261010.md</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>15KB</t>
+          <t>37KB</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>452行</t>
+          <t>1190行</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -7359,22 +7537,22 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_意思決定支援ガイドライン第2版_MECEチェック_20261010.md</t>
+          <t>北塩原村_国予算レビュー反証確認_訂正版_20261011.md</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>34KB</t>
+          <t>20KB</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>1112行</t>
+          <t>666行</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7564,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_村HP掲載施策の整理_20261010.md</t>
+          <t>北塩原村_情報公表制度と経営情報見える化の計画反映レビュー_20261010.md</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -7396,12 +7574,12 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>233行</t>
+          <t>452行</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>村ホームページ掲載施策の棚卸し</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
@@ -7413,22 +7591,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_見込量算定RedTeam再レビュー_20261010.md</t>
+          <t>北塩原村_意思決定支援ガイドライン第2版_MECEチェック_20261010.md</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18KB</t>
+          <t>34KB</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>762行</t>
+          <t>1112行</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>見込量算定のＲｅｄＴｅａｍ</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -7440,103 +7618,103 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_高齢者児童社会福祉HPの整理_20261010.md</t>
+          <t>北塩原村_村HP掲載施策の整理_20261010.md</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>13KB</t>
+          <t>15KB</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>274行</t>
+          <t>233行</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し</t>
+          <t>村ホームページ掲載施策の棚卸し</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>他メンバー素案_20261008</t>
+          <t>レビュー_20261010</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
+          <t>北塩原村_見込量算定RedTeam再レビュー_20261010.md</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>4,613KB</t>
+          <t>18KB</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>526段落</t>
+          <t>762行</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>見込量算定のＲｅｄＴｅａｍ</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>レビュー_20261010</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
+          <t>北塩原村_高齢者児童社会福祉HPの整理_20261010.md</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>541KB</t>
+          <t>13KB</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4頁</t>
+          <t>274行</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>村ホームページ3分野の棚卸し</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>他メンバー素案_20261008</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
+          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>2,628KB</t>
+          <t>4,613KB</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>38頁</t>
+          <t>526段落</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -7548,22 +7726,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
+          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>257KB</t>
+          <t>541KB</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>4頁</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -7575,17 +7753,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
+          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>231KB</t>
+          <t>2,628KB</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>12頁</t>
+          <t>38頁</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -7602,22 +7780,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
+          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>669KB</t>
+          <t>257KB</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>74頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -7629,22 +7807,22 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
+          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>347KB</t>
+          <t>231KB</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>22頁</t>
+          <t>12頁</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -7656,22 +7834,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
+          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>719KB</t>
+          <t>669KB</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>25頁</t>
+          <t>74頁</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -7683,22 +7861,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
+          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>712KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>31頁</t>
+          <t>22頁</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
         </is>
       </c>
     </row>
@@ -7710,22 +7888,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
+          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>1,974KB</t>
+          <t>719KB</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>8頁</t>
+          <t>25頁</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／骨子案からの移植</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -7737,22 +7915,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
+          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>3,545KB</t>
+          <t>712KB</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>17頁</t>
+          <t>31頁</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7942,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
+          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>249KB</t>
+          <t>1,974KB</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -7779,7 +7957,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>令和8年法改正の反映／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -7791,22 +7969,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
+          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>170KB</t>
+          <t>3,545KB</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>11頁</t>
+          <t>17頁</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -7818,22 +7996,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>141KB</t>
+          <t>249KB</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>7頁</t>
+          <t>8頁</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
@@ -7845,76 +8023,76 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>2KB</t>
+          <t>170KB</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>19行</t>
+          <t>11頁</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>基本指針</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>265KB</t>
+          <t>141KB</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>7頁</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>障がい児の論点（法改正）</t>
+          <t>高次脳機能障害者支援法</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>基本指針</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
+          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>273KB</t>
+          <t>2KB</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>9頁</t>
+          <t>19行</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>障がい児の論点（法改正）</t>
+          <t>高次脳機能障害者支援法</t>
         </is>
       </c>
     </row>
@@ -7926,76 +8104,76 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
+          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>1,331KB</t>
+          <t>265KB</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
+          <t>障がい児の論点（法改正）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>基本指針</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
+          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>417KB</t>
+          <t>273KB</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>3頁</t>
+          <t>9頁</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
+          <t>障がい児の論点（法改正）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>基本指針</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>令和8年度住民向け成年後見講座.pdf</t>
+          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>803KB</t>
+          <t>1,331KB</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
         </is>
       </c>
     </row>
@@ -8007,167 +8185,191 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>緊急連絡カード.pdf</t>
+          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>828KB</t>
+          <t>417KB</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>1頁</t>
+          <t>3頁</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>現行計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+          <t>令和8年度住民向け成年後見講座.pdf</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>1,582KB</t>
+          <t>803KB</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
+          <t>重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>県計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+          <t>緊急連絡カード.pdf</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>187KB</t>
+          <t>828KB</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>1141行</t>
+          <t>1頁</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し</t>
+          <t>重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
+          <t>現行計画</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>1,582KB</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>63頁</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>県計画</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>187KB</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>1141行</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>村ホームページ3分野の棚卸し</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
           <t>関連計画</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>北塩原村_第10期介護保険事業計画_素案_e591fe8.md</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>422KB</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>3720行</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>エビデンスのファイルが生成器に現れない系統（4系統。なぜ現れないかを書く）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>なぜファイルが現れないか</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>第3回レビューへの対応</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>外部レビューの結果はチャットで受領したものであり、ファイルとして格納していない。指摘の全文は生成器の定数（REVIEW）に写してある</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>打合せ論点10項目</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>打合せ論点は口頭と当方の記録によるものであり、外部資料を直に開いていない</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr"/>
-      <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="9" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>関連法令3法</t>
+          <t>第3回レビューへの対応</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>災害対策基本法・障害者雇用促進法・社会福祉士及び介護福祉士法の条文は生成器の定数に写してある（原典の入手はＳ-28等で依頼中）</t>
+          <t>外部レビューの結果はチャットで受領したものであり、ファイルとして格納していない。指摘の全文は生成器の定数（REVIEW）に写してある</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
@@ -8177,23 +8379,53 @@
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>当方が作った図</t>
+          <t>打合せ論点10項目</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>図の元データは当方の算定（kitashiobara_common.py のPOPULATION・BENEFIT_YEARS 等）による</t>
+          <t>打合せ論点は口頭と当方の記録によるものであり、外部資料を直に開いていない</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr"/>
       <c r="D50" s="9" t="inlineStr"/>
       <c r="E50" s="9" t="inlineStr"/>
     </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>関連法令3法</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>災害対策基本法・障害者雇用促進法・社会福祉士及び介護福祉士法の条文は生成器の定数に写してある（原典の入手はＳ-28等で依頼中）</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>図の元データは当方の算定（kitashiobara_common.py のPOPULATION・BENEFIT_YEARS 等）による</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr"/>
+      <c r="D52" s="9" t="inlineStr"/>
+      <c r="E52" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は35系統・143件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
+          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は36系統・144件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>172</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>+712</t>
+          <t>+714</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>系統ごとの件数（35系統・143件）</t>
+          <t>系統ごとの件数（36系統・144件）</t>
         </is>
       </c>
     </row>
@@ -1761,73 +1761,103 @@
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>前期計画のレッドチーム分析</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>追記</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_zenki_redteam.py</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>前期計画が挙げたＵＤフォント・配色への配慮とほじょ犬マークが落ちていたため足した</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B48" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>図の作成</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>build_kitashiobara_graph.py</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>他メンバー版の図は画像で取り込まれており数値を直せないため、当方で作り直せる図を別に作った</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
-        <v>143</v>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>35系統</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>※ 型ごとの内訳は 追記 108件／移植 20件／図の作成 10件／書き換え 5件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>36系統</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>※ 型ごとの内訳は 追記 109件／移植 20件／図の作成 10件／書き換え 5件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
+        </is>
+      </c>
+    </row>
     <row r="52"/>
     <row r="53"/>
     <row r="54"/>
+    <row r="55"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A50:F54"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A51:F55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1839,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1854,7 +1884,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全143件</t>
+          <t>全144件</t>
         </is>
       </c>
     </row>
@@ -6826,22 +6856,22 @@
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Z-1</t>
+          <t>ＳＺ-3</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>前期計画のレッドチーム分析</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>第5章2（1）住民への情報提供等</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
@@ -6851,19 +6881,19 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文1</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>第4次北塩原村障がい者計画（通し頁20。本文頁16）１啓発・広報⑤「北塩原村広報」・ホームページ等による啓発広報</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Z-2</t>
+          <t>Z-1</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
@@ -6878,7 +6908,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>（１）給付費の推移</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -6900,7 +6930,7 @@
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Z-3</t>
+          <t>Z-2</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -6915,7 +6945,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>（３）サービス別の構成（令和７年度）</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
@@ -6930,14 +6960,14 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（各年４月１日現在）</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Z-4</t>
+          <t>Z-3</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
@@ -6952,7 +6982,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
+          <t>（１）高齢化率</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -6967,14 +6997,14 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+          <t>資料：北塩原村（各年４月１日現在）</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Z-5</t>
+          <t>Z-4</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -6989,12 +7019,12 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
+          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -7004,14 +7034,14 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章６により作成）</t>
+          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Z-6</t>
+          <t>Z-5</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
@@ -7026,7 +7056,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -7041,14 +7071,14 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+          <t>資料：北塩原村（第５章６により作成）</t>
         </is>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Z-7</t>
+          <t>Z-6</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -7063,7 +7093,7 @@
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
@@ -7078,14 +7108,14 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章２（11）により作成）</t>
+          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>Z-7</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
@@ -7100,12 +7130,12 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表の後</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -7115,14 +7145,14 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+          <t>資料：北塩原村（第５章２（11）により作成）</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Z-9</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -7137,12 +7167,12 @@
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+          <t>二つめは成年後見制度の利用を支援する事業です。</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -7152,42 +7182,79 @@
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
+          <t>Z-9</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
           <t>Z-8</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
-      <c r="C148" s="19" t="inlineStr">
+      <c r="C149" s="19" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D149" s="9" t="inlineStr">
         <is>
           <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なります。</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E149" s="10" t="inlineStr">
         <is>
           <t>表の後</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
+      <c r="F149" s="10" t="inlineStr">
         <is>
           <t>図1点</t>
         </is>
       </c>
-      <c r="G148" s="5" t="inlineStr">
+      <c r="G149" s="9" t="inlineStr">
         <is>
           <t>資料：障害者総合支援法第７条及び本計画により作成</t>
         </is>
@@ -7714,7 +7781,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8348,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は36系統・144件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
+          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は39系統・190件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
         </is>
       </c>
     </row>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>26</v>
@@ -683,12 +683,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>+714</t>
+          <t>+719</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>+117</t>
+          <t>+122</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>系統ごとの件数（36系統・144件）</t>
+          <t>系統ごとの件数（39系統・190件）</t>
         </is>
       </c>
     </row>
@@ -1791,73 +1791,163 @@
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_mura_daicho.py</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>第5章の実績の表が他メンバー版の値のままで、村の協議会資料（資料２－３）と食い違っていた。台帳の受領で裏づけが取れた</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_mura_daicho.py</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>実績の表を直したことに伴い、「見込量どおり」「利用がなかった」とする評価の文が事実と合わなくなった</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>追記</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_mura_daicho.py</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>実績の出所と、村に確かめている数え方の違い・見込量との離れを注記した</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n">
+      <c r="B51" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>図の作成</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>build_kitashiobara_graph.py</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>他メンバー版の図は画像で取り込まれており数値を直せないため、当方で作り直せる図を別に作った</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n">
-        <v>144</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="B52" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>36系統</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>※ 型ごとの内訳は 追記 109件／移植 20件／図の作成 10件／書き換え 5件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>39系統</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>※ 型ごとの内訳は 追記 114件／書き換え 46件／移植 20件／図の作成 10件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
+        </is>
+      </c>
+    </row>
     <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A54:F58"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A51:F55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1869,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1884,7 +1974,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全144件</t>
+          <t>全190件</t>
         </is>
       </c>
     </row>
@@ -6893,368 +6983,2070 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Z-1</t>
+          <t>ＤＫ-1</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>第5章 表５-４ 居宅介護（人／月）</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Z-2</t>
+          <t>ＤＫ-2</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>第5章 表５-４ 居宅介護（時間／月）</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>資料２－３</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Z-3</t>
+          <t>ＤＫ-3</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>第5章 表５-７ 生活介護（人／月）</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（各年４月１日現在）</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Z-4</t>
+          <t>ＤＫ-4</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C143" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
+          <t>第5章 表５-７ 生活介護（人日／月）</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Z-5</t>
+          <t>ＤＫ-5</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
+          <t>第5章 表５-７ 自立訓練（生活訓練）（人／月）</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章６により作成）</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Z-6</t>
+          <t>ＤＫ-6</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C145" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+          <t>第5章 表５-７ 自立訓練（生活訓練）（人日／月）</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Z-7</t>
+          <t>ＤＫ-7</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C146" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+          <t>第5章 表５-７ 就労移行支援（人／月）</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章２（11）により作成）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>ＤＫ-8</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C147" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+          <t>第5章 表５-７ 就労移行支援（人日／月）</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>Z-9</t>
+          <t>ＤＫ-9</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C148" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+          <t>第5章 表５-７ 就労継続支援Ａ型（人／月）</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>表の1行（3年度のセル）の置換</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+          <t>資料２－３</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="10" t="inlineStr">
         <is>
+          <t>ＤＫ-10</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ａ型（人日／月）</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-11</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ｂ型（人／月）</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-12</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ｂ型（人日／月）</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-13</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労定着支援（人／月）</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-14</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 短期入所（福祉型）（人／月）</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F153" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-15</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 短期入所（福祉型）（人日／月）</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-16</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-10 共同生活援助（人／月）</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-17</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-10 施設入所支援（人／月）</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-18</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-12 計画相談支援（人／月）</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="30" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-19</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 児童発達支援（人／月）</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-20</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 児童発達支援（人日／月）</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F159" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-21</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 放課後等デイサービス（人／月）</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-22</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 放課後等デイサービス（人日／月）</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-23</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 保育所等訪問支援（人／月）</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="30" customHeight="1">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-24</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 保育所等訪問支援（人日／月）</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-25</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 障がい児相談支援（人／月）</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-26</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 意思疎通支援事業（手話通訳者等派遣）</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-27</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 理解促進研修・啓発事業</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-28</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：介護・訓練支援用具</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="30" customHeight="1">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-29</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：自立生活支援用具</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-30</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：排泄管理支援用具</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-31</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：居宅生活動作補助用具</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-32</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 地域活動支援センター機能強化事業</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-33</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日中一時支援事業</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-34</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 福祉ホーム事業</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>表の1行（3年度のセル）の置換</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>資料２－３</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換１</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（1）≪実績値と評価≫（表５-４の後）</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="30" customHeight="1">
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換２</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）1段落目</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換３</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）2段落目</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換４</t>
+        </is>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（3）≪実績値と評価≫（表５-10の後）</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換５</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（4）≪実績値と評価≫（表５-12の後）</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換６</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（5）≪実績値と評価≫（表５-14の後）</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F179" s="10" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換７</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>第5章3≪実績値と評価≫（表５-29の後）2段落目</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>本文1段落の置換</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-注１</t>
+        </is>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（1）表５-４の評価の後</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>注記1</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-注２</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（2）表５-７の評価の後</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>注記1</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-注３</t>
+        </is>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C183" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（3）表５-11の見込量の後</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F183" s="10" t="inlineStr">
+        <is>
+          <t>注記1</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-注４</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C184" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（5）表５-14の評価の後</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>注記1</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-注５</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C185" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>第5章3 表５-29の評価の後</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>注記1</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Z-1</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>（１）給付費の推移</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>資料：村提供の障がいサービス給付実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="10" t="inlineStr">
+        <is>
+          <t>Z-2</t>
+        </is>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C187" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>（３）サービス別の構成（令和７年度）</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>資料：村提供の障がいサービス給付実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Z-3</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C188" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>（１）高齢化率</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（各年４月１日現在）</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>Z-4</t>
+        </is>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
+        </is>
+      </c>
+      <c r="E189" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F189" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Z-5</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C190" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章６により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="10" t="inlineStr">
+        <is>
+          <t>Z-6</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C191" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F191" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="inlineStr">
+        <is>
+          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>Z-7</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C192" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章２（11）により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="10" t="inlineStr">
+        <is>
+          <t>Z-10</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F193" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G193" s="9" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>Z-9</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C194" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="10" t="inlineStr">
+        <is>
           <t>Z-8</t>
         </is>
       </c>
-      <c r="B149" s="10" t="inlineStr">
+      <c r="B195" s="10" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
-      <c r="C149" s="19" t="inlineStr">
+      <c r="C195" s="19" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D195" s="9" t="inlineStr">
         <is>
           <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なります。</t>
         </is>
       </c>
-      <c r="E149" s="10" t="inlineStr">
+      <c r="E195" s="10" t="inlineStr">
         <is>
           <t>表の後</t>
         </is>
       </c>
-      <c r="F149" s="10" t="inlineStr">
+      <c r="F195" s="10" t="inlineStr">
         <is>
           <t>図1点</t>
         </is>
       </c>
-      <c r="G149" s="9" t="inlineStr">
+      <c r="G195" s="9" t="inlineStr">
         <is>
           <t>資料：障害者総合支援法第７条及び本計画により作成</t>
         </is>
@@ -7275,7 +9067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7288,7 +9080,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>生成器が実際に開いているエビデンス 40点</t>
+          <t>生成器が実際に開いているエビデンス 41点</t>
         </is>
       </c>
     </row>
@@ -7781,7 +9573,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -8247,27 +10039,27 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>村資料_自立支援協議会_20260525</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
+          <t>見込量と実績.pdf</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>417KB</t>
+          <t>434KB</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>3頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
+          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
         </is>
       </c>
     </row>
@@ -8279,22 +10071,22 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>令和8年度住民向け成年後見講座.pdf</t>
+          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>803KB</t>
+          <t>417KB</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>3頁</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
@@ -8306,17 +10098,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>緊急連絡カード.pdf</t>
+          <t>令和8年度住民向け成年後見講座.pdf</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>828KB</t>
+          <t>803KB</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>1頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -8328,171 +10120,198 @@
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>現行計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+          <t>緊急連絡カード.pdf</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>1,582KB</t>
+          <t>828KB</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>1頁</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
+          <t>重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>県計画</t>
+          <t>現行計画</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>187KB</t>
+          <t>1,582KB</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>1141行</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
+          <t>県計画</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>187KB</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>1141行</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>村ホームページ3分野の棚卸し</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>関連計画</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>北塩原村_第10期介護保険事業計画_素案_e591fe8.md</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>422KB</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>3720行</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>エビデンスのファイルが生成器に現れない系統（4系統。なぜ現れないかを書く）</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>なぜファイルが現れないか</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="4" t="inlineStr"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>第3回レビューへの対応</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>外部レビューの結果はチャットで受領したものであり、ファイルとして格納していない。指摘の全文は生成器の定数（REVIEW）に写してある</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>打合せ論点10項目</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>打合せ論点は口頭と当方の記録によるものであり、外部資料を直に開いていない</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr"/>
-      <c r="D50" s="9" t="inlineStr"/>
-      <c r="E50" s="9" t="inlineStr"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr"/>
+      <c r="D51" s="9" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>関連法令3法</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>災害対策基本法・障害者雇用促進法・社会福祉士及び介護福祉士法の条文は生成器の定数に写してある（原典の入手はＳ-28等で依頼中）</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>図の元データは当方の算定（kitashiobara_common.py のPOPULATION・BENEFIT_YEARS 等）による</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr"/>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="9" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A48:E48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8504,7 +10323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8517,7 +10336,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>他メンバー版の本文を直したもの 5件</t>
+          <t>他メンバー版の本文を直したもの 46件</t>
         </is>
       </c>
     </row>
@@ -8687,6 +10506,1113 @@
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>体系・工程の決定による書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-1</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-４ 居宅介護（人／月）</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>4（4）人分／4（4）人分／4（4）人分</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>3（4）人分／2.6（4）人分／2（4）人分</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-４ 居宅介護（時間／月）</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>38（40）時間分／40（40）時間分／42（40）時間分</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>22（40）時間分／30.25（40）時間分／―（40）時間分</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-3</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 生活介護（人／月）</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>6（6）人分／6（6）人分／6（6）人分</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>5.9（6）人分／5.6（6）人分／5（6）人分</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-4</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 生活介護（人日／月）</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>118（118）人日分／120（118）人日分／118（118）人日分</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>125（118）人日分／111（118）人日分／109（118）人日分</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-5</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 自立訓練（生活訓練）（人／月）</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>1（0）人分／0（0）人分／1（1）人分</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人分／1（0）人分／1（1）人分</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-6</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 自立訓練（生活訓練）（人日／月）</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>12（0）人日分／0（0）人日分／12（12）人日分</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人日分／20.25（0）人日分／22（12）人日分</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-7</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労移行支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>0（0）人分／0（0）人分／1（1）人分</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人分／0（0）人分／―（1）人分</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-8</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労移行支援（人日／月）</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>0（0）人日分／0（0）人日分／10（10）人日分</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人日分／0（0）人日分／―（10）人日分</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-9</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ａ型（人／月）</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>1（1）人分／1（1）人分／1（1）人分</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>0（1）人分／0（1）人分／―（1）人分</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-10</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ａ型（人日／月）</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>19（19）人日分／19（19）人日分／19（19）人日分</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>0（19）人日分／0（19）人日分／―（19）人日分</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-11</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ｂ型（人／月）</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>10（10）人分／11（11）人分／11（11）人分</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>12（10）人分／11.8（11）人分／11.2（11）人分</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-12</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労継続支援Ｂ型（人日／月）</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>180（183）人日分／195（200）人日分／198（200）人日分</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>224（183）人日分／199（200）人日分／208（200）人日分</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-13</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 就労定着支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>1（0）人分／0（0）人分／1（1）人分</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人分／0（0）人分／0.3（1）人分</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-14</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 短期入所（福祉型）（人／月）</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>0（0）人分／0（0）人分／0（0）人分</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>1（0）人分／1（0）人分／0.5（0）人分</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-15</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-７ 短期入所（福祉型）（人日／月）</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>0（0）人日分／0（0）人日分／0（0）人日分</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>2（0）人日分／2（0）人日分／1（0）人日分</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-16</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-10 共同生活援助（人／月）</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>8（8）人分／8（8）人分／8（8）人分</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>6.8（8）人分／8.75（8）人分／11.7（8）人分</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-17</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-10 施設入所支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>4（4）人分／4（4）人分／4（4）人分</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>4（4）人分／3.6（4）人分／4（4）人分</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-18</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-12 計画相談支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>21（22）人分／22（22）人分／22（22）人分</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>23（22）人分／25（22）人分／22（22）人分</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-19</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 児童発達支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>1（1）人分／0（0）人分／0（0）人分</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>1（1）人分／1（0）人分／―（0）人分</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-20</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 児童発達支援（人日／月）</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>7（7）人日分／0（0）人日分／0（0）人日分</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>5（7）人日分／2（0）人日分／―（0）人日分</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-21</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 放課後等デイサービス（人／月）</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>1（1）人分／1（1）人分／1（1）人分</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>1（1）人分／2.25（1）人分／―（1）人分</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-22</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 放課後等デイサービス（人日／月）</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>2（2）人日分／2（2）人日分／2（2）人日分</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>1.8（2）人日分／6.75（2）人日分／―（2）人日分</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-23</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 保育所等訪問支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>0（0）人分／0（0）人分／0（0）人分</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人分／1（0）人分／―（0）人分</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-24</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 保育所等訪問支援（人日／月）</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>0（0）人日分／0（0）人日分／0（0）人日分</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人日分／1.3（0）人日分／―（0）人日分</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-25</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-14 障がい児相談支援（人／月）</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>2（2）人分／2（2）人分／2（2）人分</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>2（2）人分／4（2）人分／―（2）人分</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-26</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 意思疎通支援事業（手話通訳者等派遣）</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>0（0）件／0（0）件／0（0）件</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>0（0）件／1（0）件／2（0）件</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-27</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 理解促進研修・啓発事業</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>0（0）件／0（0）件／0（0）件</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>0（0）件／3（0）件／―（0）件</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-28</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：介護・訓練支援用具</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>1（2）件／1（2）件／1（2）件</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>0（2）件／0（2）件／―（2）件</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-29</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：自立生活支援用具</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>1（1）件／1（1）件／1（1）件</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>0（1）件／0（1）件／―（1）件</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-30</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：排泄管理支援用具</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>72（72）件／72（72）件／72（72）件</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>75（72）件／77（72）件／72（72）件</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-31</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日常生活用具：居宅生活動作補助用具</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>0（0）件／0（0）件／0（0）件</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>1（0）件／0（0）件／0（0）件</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-32</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 地域活動支援センター機能強化事業</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>3（2）人／3（2）人／3（2）人</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>2（2）人／2（2）人／2（2）人</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ-33</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 日中一時支援事業</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>2（2）人／2（2）人／2（2）人</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>3（2）人／3（2）人／―（2）人</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-34</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>第5章 表５-29 福祉ホーム事業</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>1（0）人／1（0）人／1（0）人</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>0（0）人／0（0）人／―（0）人</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換１</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（1）≪実績値と評価≫（表５-４の後）</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>居宅介護については、令和６年度以降、見込量どおり４人の方が利用しており、サービス提供時間についても概ね見込量どおりとなりました。その他のサービスについては、計画値と同様に利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>居宅介護については、利用者が令和６年度の月３人から令和７年度は月2.6人に減り、令和８年度は年度途中までの平均で月２人です。サービス提供時間は、令和６年度が月22時間、令和７年度が月30.25時間で、見込量（月40時間）を下回りました。その他のサービスについては、計画値と同様に利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換２</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）1段落目</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>生活介護は、見込量どおり６人の方が利用しています。就労継続支援Ｂ型は、令和７年度以降11人と見込量どおりの利用となり、サービス量も概ね見込量どおりとなりました。自立訓練（生活訓練）は、令和６年度及び令和８年度に１人の利用がありました。就労移行支援は令和８年度に１人、就労定着支援は令和６年度及び令和８年度に１人の利用がありました。</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>生活介護は、令和６年度に月5.9人、令和７年度に月5.6人が利用し、令和８年度は年度途中までの平均で月５人です。就労継続支援Ｂ型は、令和６年度に月12人、令和７年度に月11.8人と見込量（令和６年度10人、令和７年度11人）を上回り、サービス量も令和６年度は月224人日と見込量（月183人日）を上回りました。自立訓練（生活訓練）は、令和７年度から１人の利用があります。就労移行支援及び就労継続支援Ａ型は、令和７年度までの利用はありませんでした。就労定着支援は、令和８年度の途中から１人の利用があります。</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換３</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）2段落目</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>令和７年10月に開始された就労選択支援については、令和８年度までの利用はありませんでした。また、短期入所については、第７期計画と同様に利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>令和７年10月に開始された就労選択支援については、令和８年度までの利用はありませんでした。また、短期入所（福祉型）は、第７期計画では見込んでいませんでしたが、令和６年度から令和８年度まで毎年度利用がありました。</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換４</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（3）≪実績値と評価≫（表５-10の後）</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>共同生活援助は、令和６年度以降８人の方が利用しており、見込量どおりとなりました。施設入所支援の実績値については、計画値と同値の４人となりました。自立生活援助については、利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>共同生活援助は、利用者が令和６年度の月6.8人から、令和７年度は月8.75人、令和８年度は年度途中までの平均で月11.7人と増えており、令和７年度以降は見込量（８人）を上回っています。施設入所支援は、令和６年度が４人、令和７年度が月3.6人で、令和７年度末は４人でした。自立生活援助については、利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換５</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（4）≪実績値と評価≫（表５-12の後）</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>計画相談支援については、令和６年度が21人、令和７年度以降は22人と、概ね見込量どおりの利用となりました。地域移行支援及び地域定着支援については、実績がない状況です。</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>計画相談支援は、令和６年度が23人、令和７年度が25人と見込量（22人）を上回り、令和８年度は年度途中までに22人が利用しています。この人数は、年度の中で計画の作成又はモニタリングを受けた方の実人数です。毎月の請求で数えると、月に６人から７人程度です。地域移行支援及び地域定着支援については、実績がない状況です。</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ書換６</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（5）≪実績値と評価≫（表５-14の後）</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>児童発達支援については、令和６年度に１人の利用がありましたが、対象児童が地域の幼稚園に通園するようになったことから、令和７年度以降の利用はありませんでした。放課後等デイサービス及び障がい児相談支援については、見込量どおりの利用となりました。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>ＤＫ書換７</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>第5章3≪実績値と評価≫（表５-29の後）2段落目</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>日常生活用具給付事業の排泄管理支援用具については、見込量どおりの給付となりました。また、地域活動支援センター機能強化事業及び福祉ホーム事業は見込量を上回る利用があり、日中一時支援事業は見込量どおりの利用となりました。一方、理解促進研修・啓発事業、自発的活動支援事業、意思疎通支援事業及び移動支援事業については、実績がありませんでした。</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>日常生活用具給付事業の排泄管理支援用具は、令和６年度が75件、令和７年度が77件と、見込量（72件）を上回りました。居宅生活動作補助用具は令和６年度に１件の給付がありましたが、介護・訓練支援用具及び自立生活支援用具の給付はありませんでした。地域活動支援センター機能強化事業は見込量どおり２人が利用しており、令和７年12月からは利用の日数が月平均７日程度から19日程度に増えています。日中一時支援事業は、３人の支給決定に対し、毎月の利用は１人程度です。意思疎通支援事業は令和７年度に１件、令和８年度に２件の利用があり、理解促進研修・啓発事業は令和７年度に３件を実施しました。一方、自発的活動支援事業及び移動支援事業については実績がなく、福祉ホーム事業についても令和７年度までの実績はありませんでした。</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は39系統・190件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
+          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は40系統・194件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
         </is>
       </c>
     </row>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>26</v>
@@ -683,12 +683,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>+719</t>
+          <t>+721</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>+122</t>
+          <t>+124</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>系統ごとの件数（39系統・190件）</t>
+          <t>系統ごとの件数（40系統・194件）</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
@@ -1881,71 +1881,101 @@
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>書き換え</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_tasha_review.py</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>第3章冒頭が村の計画策定方針（中間見直しを行う）と食い違っていた</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月23日</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B52" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>図の作成</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>build_kitashiobara_graph.py</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>他メンバー版の図は画像で取り込まれており数値を直せないため、当方で作り直せる図を別に作った</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
-        <v>190</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="B53" s="6" t="n">
+        <v>194</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>39系統</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>※ 型ごとの内訳は 追記 114件／書き換え 46件／移植 20件／図の作成 10件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>40系統</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>※ 型ごとの内訳は 追記 116件／書き換え 48件／移植 20件／図の作成 10件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
+        </is>
+      </c>
+    </row>
     <row r="56"/>
     <row r="57"/>
     <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A54:F58"/>
+    <mergeCell ref="A55:F59"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
   </mergeCells>
@@ -1959,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1974,7 +2004,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全190件</t>
+          <t>全194件</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8271,7 @@
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換１</t>
+          <t>ＤＫ-35</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
@@ -8251,12 +8281,12 @@
       </c>
       <c r="C174" s="18" t="inlineStr">
         <is>
-          <t>村提供の給付の台帳による評価の文の書き換え</t>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>第5章1（1）≪実績値と評価≫（表５-４の後）</t>
+          <t>第4章 成果目標（福祉施設から一般就労への移行等） 令和６年度末の就労定着支援事業の利用者数</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -8266,19 +8296,19 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>本文1段落の置換</t>
+          <t>表の1行（数値のセル）の置換</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ書換２</t>
+          <t>ＤＫ書換１</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
@@ -8293,7 +8323,7 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>第5章1（2）≪実績値と評価≫（表５-７の後）1段落目</t>
+          <t>第5章1（1）≪実績値と評価≫（表５-４の後）</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
@@ -8315,7 +8345,7 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換３</t>
+          <t>ＤＫ書換２</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
@@ -8330,7 +8360,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>第5章1（2）≪実績値と評価≫（表５-７の後）2段落目</t>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）1段落目</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -8352,7 +8382,7 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ書換４</t>
+          <t>ＤＫ書換３</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
@@ -8367,7 +8397,7 @@
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>第5章1（3）≪実績値と評価≫（表５-10の後）</t>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）2段落目</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
@@ -8389,7 +8419,7 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換５</t>
+          <t>ＤＫ書換４</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
@@ -8404,7 +8434,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>第5章1（4）≪実績値と評価≫（表５-12の後）</t>
+          <t>第5章1（3）≪実績値と評価≫（表５-10の後）</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -8426,7 +8456,7 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ書換６</t>
+          <t>ＤＫ書換５</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
@@ -8441,7 +8471,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>第5章1（5）≪実績値と評価≫（表５-14の後）</t>
+          <t>第5章1（4）≪実績値と評価≫（表５-12の後）</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
@@ -8463,7 +8493,7 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換７</t>
+          <t>ＤＫ書換６</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
@@ -8478,7 +8508,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>第5章3≪実績値と評価≫（表５-29の後）2段落目</t>
+          <t>第5章1（5）≪実績値と評価≫（表５-14の後）</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -8500,7 +8530,7 @@
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ-注１</t>
+          <t>ＤＫ書換７</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
@@ -8508,36 +8538,36 @@
           <t>令和８年10月22日</t>
         </is>
       </c>
-      <c r="C181" s="17" t="inlineStr">
-        <is>
-          <t>村提供の給付の台帳の注記</t>
+      <c r="C181" s="18" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>第5章1（1）表５-４の評価の後</t>
+          <t>第5章3≪実績値と評価≫（表５-29の後）2段落目</t>
         </is>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
         <is>
-          <t>注記1</t>
+          <t>本文1段落の置換</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ-注２</t>
+          <t>ＤＫ-注１</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
@@ -8552,7 +8582,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>第5章1（2）表５-７の評価の後</t>
+          <t>第5章1（1）表５-４の評価の後</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -8574,7 +8604,7 @@
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ-注３</t>
+          <t>ＤＫ-注２</t>
         </is>
       </c>
       <c r="B183" s="10" t="inlineStr">
@@ -8589,7 +8619,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>第5章1（3）表５-11の見込量の後</t>
+          <t>第5章1（2）表５-７の評価の後</t>
         </is>
       </c>
       <c r="E183" s="10" t="inlineStr">
@@ -8611,7 +8641,7 @@
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ-注４</t>
+          <t>ＤＫ-注３</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
@@ -8626,7 +8656,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>第5章1（5）表５-14の評価の後</t>
+          <t>第5章1（3）表５-11の見込量の後</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -8648,7 +8678,7 @@
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ-注５</t>
+          <t>ＤＫ-注４</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
@@ -8663,7 +8693,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>第5章3 表５-29の評価の後</t>
+          <t>第5章1（5）表５-14の評価の後</t>
         </is>
       </c>
       <c r="E185" s="10" t="inlineStr">
@@ -8685,22 +8715,22 @@
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>Z-1</t>
+          <t>ＤＫ-注５</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C186" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>第5章3 表５-29の評価の後</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -8710,34 +8740,34 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>注記1</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
         </is>
       </c>
     </row>
     <row r="187" ht="30" customHeight="1">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>Z-2</t>
+          <t>ＤＫ-注６</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C187" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>第4章 福祉施設から一般就労への移行等（目標の本文の後）</t>
         </is>
       </c>
       <c r="E187" s="10" t="inlineStr">
@@ -8747,34 +8777,34 @@
       </c>
       <c r="F187" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>注記1</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
         </is>
       </c>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>Z-3</t>
+          <t>ＤＫ-注７</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C188" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>第5章1（4）表５-13の見込量の後</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -8784,56 +8814,56 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>注記1</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（各年４月１日現在）</t>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
         </is>
       </c>
     </row>
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>Z-4</t>
+          <t>ＴＲ書換１</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C189" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月23日</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
+          <t>第3章 冒頭（第４次北塩原村障がい者計画の位置づけ）</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文1段落の置換</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/計画策定方針.pdf</t>
         </is>
       </c>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Z-5</t>
+          <t>Z-1</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
@@ -8848,12 +8878,12 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
+          <t>（１）給付費の推移</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
@@ -8863,14 +8893,14 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章６により作成）</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>Z-6</t>
+          <t>Z-2</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
@@ -8885,12 +8915,12 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+          <t>（３）サービス別の構成（令和７年度）</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
@@ -8900,14 +8930,14 @@
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Z-7</t>
+          <t>Z-3</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
@@ -8922,12 +8952,12 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+          <t>（１）高齢化率</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
@@ -8937,14 +8967,14 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章２（11）により作成）</t>
+          <t>資料：北塩原村（各年４月１日現在）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>Z-4</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
@@ -8959,7 +8989,7 @@
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
@@ -8974,14 +9004,14 @@
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
         </is>
       </c>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>Z-9</t>
+          <t>Z-5</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
@@ -8996,7 +9026,7 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -9011,42 +9041,190 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+          <t>資料：北塩原村（第５章６により作成）</t>
         </is>
       </c>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="10" t="inlineStr">
         <is>
+          <t>Z-6</t>
+        </is>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F195" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G195" s="9" t="inlineStr">
+        <is>
+          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>Z-7</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C196" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章２（11）により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="10" t="inlineStr">
+        <is>
+          <t>Z-10</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+        </is>
+      </c>
+      <c r="E197" s="10" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="F197" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G197" s="9" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>Z-9</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C198" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="10" t="inlineStr">
+        <is>
           <t>Z-8</t>
         </is>
       </c>
-      <c r="B195" s="10" t="inlineStr">
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
-      <c r="C195" s="19" t="inlineStr">
+      <c r="C199" s="19" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="D195" s="9" t="inlineStr">
+      <c r="D199" s="9" t="inlineStr">
         <is>
           <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なります。</t>
         </is>
       </c>
-      <c r="E195" s="10" t="inlineStr">
+      <c r="E199" s="10" t="inlineStr">
         <is>
           <t>表の後</t>
         </is>
       </c>
-      <c r="F195" s="10" t="inlineStr">
+      <c r="F199" s="10" t="inlineStr">
         <is>
           <t>図1点</t>
         </is>
       </c>
-      <c r="G195" s="9" t="inlineStr">
+      <c r="G199" s="9" t="inlineStr">
         <is>
           <t>資料：障害者総合支援法第７条及び本計画により作成</t>
         </is>
@@ -9067,7 +9245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9080,7 +9258,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>生成器が実際に開いているエビデンス 41点</t>
+          <t>生成器が実際に開いているエビデンス 44点</t>
         </is>
       </c>
     </row>
@@ -9553,81 +9731,81 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>他メンバー素案_20261008</t>
+          <t>他AIレビュー_20261023</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
+          <t>北塩原村_見込量・KPI_RedTeamレビュー.docx</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>4,613KB</t>
+          <t>48KB</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>526段落</t>
+          <t>60段落</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>他AIレビュー_20261023</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
+          <t>国基本指針_根拠対応表_作成資料.pdf</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>541KB</t>
+          <t>172KB</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4頁</t>
+          <t>1頁</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>他メンバー素案_20261008</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
+          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>2,628KB</t>
+          <t>4,613KB</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>38頁</t>
+          <t>526段落</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -9639,22 +9817,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
+          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>257KB</t>
+          <t>541KB</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>4頁</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -9666,17 +9844,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
+          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>231KB</t>
+          <t>2,628KB</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>12頁</t>
+          <t>38頁</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -9693,22 +9871,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
+          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>669KB</t>
+          <t>257KB</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>74頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -9720,22 +9898,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
+          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>347KB</t>
+          <t>231KB</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>22頁</t>
+          <t>12頁</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9925,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
+          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>719KB</t>
+          <t>669KB</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>25頁</t>
+          <t>74頁</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -9774,22 +9952,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
+          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>712KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>31頁</t>
+          <t>22頁</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
         </is>
       </c>
     </row>
@@ -9801,22 +9979,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
+          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>1,974KB</t>
+          <t>719KB</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>8頁</t>
+          <t>25頁</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／骨子案からの移植</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -9828,22 +10006,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
+          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>3,545KB</t>
+          <t>712KB</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>17頁</t>
+          <t>31頁</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -9855,12 +10033,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
+          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>249KB</t>
+          <t>1,974KB</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -9870,7 +10048,7 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>令和8年法改正の反映／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -9882,22 +10060,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
+          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>170KB</t>
+          <t>3,545KB</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>11頁</t>
+          <t>17頁</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -9909,22 +10087,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>141KB</t>
+          <t>249KB</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>7頁</t>
+          <t>8頁</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
@@ -9936,76 +10114,76 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>2KB</t>
+          <t>170KB</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>19行</t>
+          <t>11頁</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>基本指針</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>265KB</t>
+          <t>141KB</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>7頁</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>障がい児の論点（法改正）</t>
+          <t>高次脳機能障害者支援法</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>基本指針</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
+          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>273KB</t>
+          <t>2KB</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>9頁</t>
+          <t>19行</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>障がい児の論点（法改正）</t>
+          <t>高次脳機能障害者支援法</t>
         </is>
       </c>
     </row>
@@ -10017,93 +10195,93 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
+          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>1,331KB</t>
+          <t>265KB</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
+          <t>障がい児の論点（法改正）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>村資料_自立支援協議会_20260525</t>
+          <t>基本指針</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>見込量と実績.pdf</t>
+          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>434KB</t>
+          <t>273KB</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>9頁</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
+          <t>障がい児の論点（法改正）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>基本指針</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
+          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>417KB</t>
+          <t>1,331KB</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>3頁</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>村資料_自立支援協議会_20260525</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>令和8年度住民向け成年後見講座.pdf</t>
+          <t>見込量と実績.pdf</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>803KB</t>
+          <t>434KB</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -10113,205 +10291,286 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>村資料_自立支援協議会_20260525</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>緊急連絡カード.pdf</t>
+          <t>計画策定方針.pdf</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>828KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>1頁</t>
+          <t>5頁</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／論点メモ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>現行計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>1,582KB</t>
+          <t>417KB</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>3頁</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
+          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>県計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+          <t>令和8年度住民向け成年後見講座.pdf</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>187KB</t>
+          <t>803KB</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>1141行</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し</t>
+          <t>重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>村資料_高齢者施策_20261010</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>緊急連絡カード.pdf</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>828KB</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>1頁</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>重点施策12件の評価設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>現行計画</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>1,582KB</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>63頁</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>県計画</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>187KB</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>1141行</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>村ホームページ3分野の棚卸し</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
           <t>関連計画</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>北塩原村_第10期介護保険事業計画_素案_e591fe8.md</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>422KB</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>3720行</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>エビデンスのファイルが生成器に現れない系統（4系統。なぜ現れないかを書く）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>なぜファイルが現れないか</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>第3回レビューへの対応</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>外部レビューの結果はチャットで受領したものであり、ファイルとして格納していない。指摘の全文は生成器の定数（REVIEW）に写してある</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>打合せ論点10項目</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>打合せ論点は口頭と当方の記録によるものであり、外部資料を直に開いていない</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr"/>
-      <c r="D51" s="9" t="inlineStr"/>
-      <c r="E51" s="9" t="inlineStr"/>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr"/>
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>関連法令3法</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>災害対策基本法・障害者雇用促進法・社会福祉士及び介護福祉士法の条文は生成器の定数に写してある（原典の入手はＳ-28等で依頼中）</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>図の元データは当方の算定（kitashiobara_common.py のPOPULATION・BENEFIT_YEARS 等）による</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr"/>
-      <c r="D53" s="9" t="inlineStr"/>
-      <c r="E53" s="9" t="inlineStr"/>
+      <c r="C56" s="9" t="inlineStr"/>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A51:E51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10323,7 +10582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10336,7 +10595,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>他メンバー版の本文を直したもの 46件</t>
+          <t>他メンバー版の本文を直したもの 48件</t>
         </is>
       </c>
     </row>
@@ -11430,49 +11689,49 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ書換１</t>
+          <t>ＤＫ-35</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>第5章1（1）≪実績値と評価≫（表５-４の後）</t>
+          <t>第4章 成果目標（福祉施設から一般就労への移行等） 令和６年度末の就労定着支援事業の利用者数</t>
         </is>
       </c>
       <c r="C45" s="22" t="inlineStr">
         <is>
-          <t>居宅介護については、令和６年度以降、見込量どおり４人の方が利用しており、サービス提供時間についても概ね見込量どおりとなりました。その他のサービスについては、計画値と同様に利用がありませんでした。</t>
+          <t>１人／令和６年度末の就労定着支援事業の利用者数</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>居宅介護については、利用者が令和６年度の月３人から令和７年度は月2.6人に減り、令和８年度は年度途中までの平均で月２人です。サービス提供時間は、令和６年度が月22時間、令和７年度が月30.25時間で、見込量（月40時間）を下回りました。その他のサービスについては、計画値と同様に利用がありませんでした。</t>
+          <t>０人／令和６年度末の就労定着支援事業の利用者数</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>村提供の給付の台帳による評価の文の書き換え</t>
+          <t>村提供の給付の台帳による実績の表の書き換え</t>
         </is>
       </c>
     </row>
     <row r="46" ht="64" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換２</t>
+          <t>ＤＫ書換１</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>第5章1（2）≪実績値と評価≫（表５-７の後）1段落目</t>
+          <t>第5章1（1）≪実績値と評価≫（表５-４の後）</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>生活介護は、見込量どおり６人の方が利用しています。就労継続支援Ｂ型は、令和７年度以降11人と見込量どおりの利用となり、サービス量も概ね見込量どおりとなりました。自立訓練（生活訓練）は、令和６年度及び令和８年度に１人の利用がありました。就労移行支援は令和８年度に１人、就労定着支援は令和６年度及び令和８年度に１人の利用がありました。</t>
+          <t>居宅介護については、令和６年度以降、見込量どおり４人の方が利用しており、サービス提供時間についても概ね見込量どおりとなりました。その他のサービスについては、計画値と同様に利用がありませんでした。</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>生活介護は、令和６年度に月5.9人、令和７年度に月5.6人が利用し、令和８年度は年度途中までの平均で月５人です。就労継続支援Ｂ型は、令和６年度に月12人、令和７年度に月11.8人と見込量（令和６年度10人、令和７年度11人）を上回り、サービス量も令和６年度は月224人日と見込量（月183人日）を上回りました。自立訓練（生活訓練）は、令和７年度から１人の利用があります。就労移行支援及び就労継続支援Ａ型は、令和７年度までの利用はありませんでした。就労定着支援は、令和８年度の途中から１人の利用があります。</t>
+          <t>居宅介護については、利用者が令和６年度の月３人から令和７年度は月2.6人に減り、令和８年度は年度途中までの平均で月２人です。サービス提供時間は、令和６年度が月22時間、令和７年度が月30.25時間で、見込量（月40時間）を下回りました。その他のサービスについては、計画値と同様に利用がありませんでした。</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -11484,22 +11743,22 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ書換３</t>
+          <t>ＤＫ書換２</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>第5章1（2）≪実績値と評価≫（表５-７の後）2段落目</t>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）1段落目</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>令和７年10月に開始された就労選択支援については、令和８年度までの利用はありませんでした。また、短期入所については、第７期計画と同様に利用がありませんでした。</t>
+          <t>生活介護は、見込量どおり６人の方が利用しています。就労継続支援Ｂ型は、令和７年度以降11人と見込量どおりの利用となり、サービス量も概ね見込量どおりとなりました。自立訓練（生活訓練）は、令和６年度及び令和８年度に１人の利用がありました。就労移行支援は令和８年度に１人、就労定着支援は令和６年度及び令和８年度に１人の利用がありました。</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>令和７年10月に開始された就労選択支援については、令和８年度までの利用はありませんでした。また、短期入所（福祉型）は、第７期計画では見込んでいませんでしたが、令和６年度から令和８年度まで毎年度利用がありました。</t>
+          <t>生活介護は、令和６年度に月5.9人、令和７年度に月5.6人が利用し、令和８年度は年度途中までの平均で月５人です。就労継続支援Ｂ型は、令和６年度に月12人、令和７年度に月11.8人と見込量（令和６年度10人、令和７年度11人）を上回り、サービス量も令和６年度は月224人日と見込量（月183人日）を上回りました。自立訓練（生活訓練）は、令和７年度から１人の利用があります。就労移行支援及び就労継続支援Ａ型は、令和７年度までの利用はありませんでした。就労定着支援は、令和８年度の途中から１人の利用があります。</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -11511,22 +11770,22 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換４</t>
+          <t>ＤＫ書換３</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第5章1（3）≪実績値と評価≫（表５-10の後）</t>
+          <t>第5章1（2）≪実績値と評価≫（表５-７の後）2段落目</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>共同生活援助は、令和６年度以降８人の方が利用しており、見込量どおりとなりました。施設入所支援の実績値については、計画値と同値の４人となりました。自立生活援助については、利用がありませんでした。</t>
+          <t>令和７年10月に開始された就労選択支援については、令和８年度までの利用はありませんでした。また、短期入所については、第７期計画と同様に利用がありませんでした。</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>共同生活援助は、利用者が令和６年度の月6.8人から、令和７年度は月8.75人、令和８年度は年度途中までの平均で月11.7人と増えており、令和７年度以降は見込量（８人）を上回っています。施設入所支援は、令和６年度が４人、令和７年度が月3.6人で、令和７年度末は４人でした。自立生活援助については、利用がありませんでした。</t>
+          <t>令和７年10月に開始された就労選択支援については、令和８年度までの利用はありませんでした。また、短期入所（福祉型）は、第７期計画では見込んでいませんでしたが、令和６年度から令和８年度まで毎年度利用がありました。</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -11538,22 +11797,22 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>ＤＫ書換５</t>
+          <t>ＤＫ書換４</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>第5章1（4）≪実績値と評価≫（表５-12の後）</t>
+          <t>第5章1（3）≪実績値と評価≫（表５-10の後）</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>計画相談支援については、令和６年度が21人、令和７年度以降は22人と、概ね見込量どおりの利用となりました。地域移行支援及び地域定着支援については、実績がない状況です。</t>
+          <t>共同生活援助は、令和６年度以降８人の方が利用しており、見込量どおりとなりました。施設入所支援の実績値については、計画値と同値の４人となりました。自立生活援助については、利用がありませんでした。</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>計画相談支援は、令和６年度が23人、令和７年度が25人と見込量（22人）を上回り、令和８年度は年度途中までに22人が利用しています。この人数は、年度の中で計画の作成又はモニタリングを受けた方の実人数です。毎月の請求で数えると、月に６人から７人程度です。地域移行支援及び地域定着支援については、実績がない状況です。</t>
+          <t>共同生活援助は、利用者が令和６年度の月6.8人から、令和７年度は月8.75人、令和８年度は年度途中までの平均で月11.7人と増えており、令和７年度以降は見込量（８人）を上回っています。施設入所支援は、令和６年度が４人、令和７年度が月3.6人で、令和７年度末は４人でした。自立生活援助については、利用がありませんでした。</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -11565,22 +11824,22 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ書換６</t>
+          <t>ＤＫ書換５</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>第5章1（5）≪実績値と評価≫（表５-14の後）</t>
+          <t>第5章1（4）≪実績値と評価≫（表５-12の後）</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>児童発達支援については、令和６年度に１人の利用がありましたが、対象児童が地域の幼稚園に通園するようになったことから、令和７年度以降の利用はありませんでした。放課後等デイサービス及び障がい児相談支援については、見込量どおりの利用となりました。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+          <t>計画相談支援については、令和６年度が21人、令和７年度以降は22人と、概ね見込量どおりの利用となりました。地域移行支援及び地域定着支援については、実績がない状況です。</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+          <t>計画相談支援は、令和６年度が23人、令和７年度が25人と見込量（22人）を上回り、令和８年度は年度途中までに22人が利用しています。この人数は、年度の中で計画の作成又はモニタリングを受けた方の実人数です。毎月の請求で数えると、月に６人から７人程度です。地域移行支援及び地域定着支援については、実績がない状況です。</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -11592,27 +11851,81 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
+          <t>ＤＫ書換６</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>第5章1（5）≪実績値と評価≫（表５-14の後）</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>児童発達支援については、令和６年度に１人の利用がありましたが、対象児童が地域の幼稚園に通園するようになったことから、令和７年度以降の利用はありませんでした。放課後等デイサービス及び障がい児相談支援については、見込量どおりの利用となりました。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>ＤＫ書換７</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>第5章3≪実績値と評価≫（表５-29の後）2段落目</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>日常生活用具給付事業の排泄管理支援用具については、見込量どおりの給付となりました。また、地域活動支援センター機能強化事業及び福祉ホーム事業は見込量を上回る利用があり、日中一時支援事業は見込量どおりの利用となりました。一方、理解促進研修・啓発事業、自発的活動支援事業、意思疎通支援事業及び移動支援事業については、実績がありませんでした。</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>日常生活用具給付事業の排泄管理支援用具は、令和６年度が75件、令和７年度が77件と、見込量（72件）を上回りました。居宅生活動作補助用具は令和６年度に１件の給付がありましたが、介護・訓練支援用具及び自立生活支援用具の給付はありませんでした。地域活動支援センター機能強化事業は見込量どおり２人が利用しており、令和７年12月からは利用の日数が月平均７日程度から19日程度に増えています。日中一時支援事業は、３人の支給決定に対し、毎月の利用は１人程度です。意思疎通支援事業は令和７年度に１件、令和８年度に２件の利用があり、理解促進研修・啓発事業は令和７年度に３件を実施しました。一方、自発的活動支援事業及び移動支援事業については実績がなく、福祉ホーム事業についても令和７年度までの実績はありませんでした。</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>村提供の給付の台帳による評価の文の書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>ＴＲ書換１</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>第3章 冒頭（第４次北塩原村障がい者計画の位置づけ）</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>「第４次北塩原村障がい者計画」（令和６年度～令和11年度）は、本計画と一体的に推進する計画であり、今回の見直しの対象ではありませんが、その基本理念・基本目標・目標値は、本計画と同じ令和11年度を目標年度としています。ここでは、その内容と本計画期間における主な取組みを整理します。</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>「第４次北塩原村障がい者計画」（令和６年度～令和11年度）は、本計画と一体的に推進する計画であり、本計画の策定にあわせて中間見直しを行います（第１章２）。その基本理念・基本目標・目標値は、本計画と同じ令和11年度を目標年度としています。ここでは、その内容と本計画期間における主な取組みを整理し、基本施策ごとの目標値の達成状況を確認します。</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>1（1）人分／1（0）人分／―（0）人分</t>
+          <t>1（1）人分／1（0）人分／1（0）人分</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>5（7）人日分／2（0）人日分／―（0）人日分</t>
+          <t>5（7）人日分／2（0）人日分／3（0）人日分</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>0（0）人分／1（0）人分／―（0）人分</t>
+          <t>0（0）人分／1（0）人分／0.8（0）人分</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>0（0）人日分／1.3（0）人日分／―（0）人日分</t>
+          <t>0（0）人日分／1.3（0）人日分／1（0）人日分</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>2（2）人分／4（2）人分／―（2）人分</t>
+          <t>2（2）人分／4（2）人分／4（2）人分</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。令和８年度は、年度途中までに児童発達支援に１人、保育所等訪問支援に１人、障がい児相談支援に４人の利用があります。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">

--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -608,7 +608,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は40系統・194件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
+          <t>他メンバーが作成された素案（令和8年10月8日受領）に対し、当方は40系統・195件の対応を行いました。件数・箇所・根拠はすべて各系統の単一出所から読み込んでおり、このブックで書き写していません。基準日：令和8年10月19日。</t>
         </is>
       </c>
     </row>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>26</v>
@@ -683,12 +683,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>+721</t>
+          <t>+722</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>+124</t>
+          <t>+125</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>系統ごとの件数（40系統・194件）</t>
+          <t>系統ごとの件数（40系統・195件）</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>※ 型ごとの内訳は 追記 116件／書き換え 48件／移植 20件／図の作成 10件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
+          <t>※ 型ごとの内訳は 追記 117件／書き換え 48件／移植 20件／図の作成 10件 です。「移植」は当方が先に作っていた骨子案の中身を他メンバー版の該当箇所へ移したもので、素案に無かった章節を足しています。「書き換え」は他メンバー版の本文が事実として誤っているものに限っており、挿入ではなく置換であるため、直す前の文が本文にちょうど1つあることを確かめてから書き換えています。当方が書いた文の誤りは、本文を書き換えるのではなく生成器の側を直しています。</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2004,7 +2004,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全194件</t>
+          <t>全195件</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>ＤＫ-注７</t>
+          <t>ＤＫ-注８</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>第5章1（4）表５-13の見込量の後</t>
+          <t>第5章1（5）表５-15の見込量の後</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -8826,81 +8826,81 @@
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>ＴＲ書換１</t>
+          <t>ＤＫ-注７</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>令和８年10月23日</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
+          <t>令和８年10月22日</t>
+        </is>
+      </c>
+      <c r="C189" s="17" t="inlineStr">
+        <is>
+          <t>村提供の給付の台帳の注記</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>第3章 冒頭（第４次北塩原村障がい者計画の位置づけ）</t>
+          <t>第5章1（4）表５-13の見込量の後</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>書き換え</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
         <is>
-          <t>本文1段落の置換</t>
+          <t>注記1</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/計画策定方針.pdf</t>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/見込量と実績.pdf</t>
         </is>
       </c>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Z-1</t>
+          <t>ＴＲ書換１</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月10日</t>
-        </is>
-      </c>
-      <c r="C190" s="19" t="inlineStr">
-        <is>
-          <t>当方が作った図</t>
+          <t>令和８年10月23日</t>
+        </is>
+      </c>
+      <c r="C190" s="18" t="inlineStr">
+        <is>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>第3章 冒頭（第４次北塩原村障がい者計画の位置づけ）</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>書き換え</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>図1点</t>
+          <t>本文1段落の置換</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>/home/user/repository/source/村資料_自立支援協議会_20260525/計画策定方針.pdf</t>
         </is>
       </c>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>Z-2</t>
+          <t>Z-1</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>（１）給付費の推移</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Z-3</t>
+          <t>Z-2</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>（３）サービス別の構成（令和７年度）</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -8967,14 +8967,14 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（各年４月１日現在）</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>Z-4</t>
+          <t>Z-3</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
+          <t>（１）高齢化率</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+          <t>資料：北塩原村（各年４月１日現在）</t>
         </is>
       </c>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>Z-5</t>
+          <t>Z-4</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
+          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設定しています。本計画期間においては、障がい福祉サービス等の提供体制の確保と合わせて、次の取組みを進め、目標の達成を目指します。</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
@@ -9041,14 +9041,14 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章６により作成）</t>
+          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
         </is>
       </c>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t>Z-6</t>
+          <t>Z-5</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
+          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で完結する支援は限られます。</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
@@ -9078,14 +9078,14 @@
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
+          <t>資料：北塩原村（第５章６により作成）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>Z-7</t>
+          <t>Z-6</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
+          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門的人材の確保及び養成、地域の体制づくりの５つの機能が求められています。</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -9115,14 +9115,14 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章２（11）により作成）</t>
+          <t>資料：国の基本指針 第二 五及び北塩原村の資料により作成</t>
         </is>
       </c>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>Z-7</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>二つめは成年後見制度の利用を支援する事業です。</t>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表の後</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
@@ -9152,14 +9152,14 @@
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
+          <t>資料：北塩原村（第５章２（11）により作成）</t>
         </is>
       </c>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>Z-9</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+          <t>二つめは成年後見制度の利用を支援する事業です。</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>表の後</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
@@ -9189,42 +9189,79 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="30" customHeight="1">
       <c r="A199" s="10" t="inlineStr">
         <is>
+          <t>Z-9</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>令和８年10月10日</t>
+        </is>
+      </c>
+      <c r="C199" s="19" t="inlineStr">
+        <is>
+          <t>当方が作った図</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>障がい福祉サービスは、一定の年齢に達することにより、対象となる制度が変わります。</t>
+        </is>
+      </c>
+      <c r="E199" s="10" t="inlineStr">
+        <is>
+          <t>表の後</t>
+        </is>
+      </c>
+      <c r="F199" s="10" t="inlineStr">
+        <is>
+          <t>図1点</t>
+        </is>
+      </c>
+      <c r="G199" s="9" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="30" customHeight="1">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
           <t>Z-8</t>
         </is>
       </c>
-      <c r="B199" s="10" t="inlineStr">
+      <c r="B200" s="6" t="inlineStr">
         <is>
           <t>令和８年10月10日</t>
         </is>
       </c>
-      <c r="C199" s="19" t="inlineStr">
+      <c r="C200" s="19" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="D199" s="9" t="inlineStr">
+      <c r="D200" s="5" t="inlineStr">
         <is>
           <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なります。</t>
         </is>
       </c>
-      <c r="E199" s="10" t="inlineStr">
+      <c r="E200" s="6" t="inlineStr">
         <is>
           <t>表の後</t>
         </is>
       </c>
-      <c r="F199" s="10" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <t>図1点</t>
         </is>
       </c>
-      <c r="G199" s="9" t="inlineStr">
+      <c r="G200" s="5" t="inlineStr">
         <is>
           <t>資料：障害者総合支援法第７条及び本計画により作成</t>
         </is>
@@ -9245,7 +9282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9258,7 +9295,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>生成器が実際に開いているエビデンス 44点</t>
+          <t>生成器が実際に開いているエビデンス 45点</t>
         </is>
       </c>
     </row>
@@ -9785,54 +9822,54 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>他メンバー素案_20261008</t>
+          <t>他AIレビュー_20261023_第2回</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
+          <t>レビュー結果_本文.md</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>4,613KB</t>
+          <t>14KB</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>526段落</t>
+          <t>111行</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>他メンバー素案_20261008</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
+          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>541KB</t>
+          <t>4,613KB</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>4頁</t>
+          <t>526段落</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -9844,22 +9881,22 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
+          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>2,628KB</t>
+          <t>541KB</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>38頁</t>
+          <t>4頁</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -9871,17 +9908,17 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
+          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>257KB</t>
+          <t>2,628KB</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>38頁</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -9898,17 +9935,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
+          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>231KB</t>
+          <t>257KB</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>12頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -9925,22 +9962,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
+          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>669KB</t>
+          <t>231KB</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>74頁</t>
+          <t>12頁</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -9952,22 +9989,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
+          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>347KB</t>
+          <t>669KB</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>22頁</t>
+          <t>74頁</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -9979,22 +10016,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
+          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>719KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>25頁</t>
+          <t>22頁</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
         </is>
       </c>
     </row>
@@ -10006,17 +10043,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
+          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>712KB</t>
+          <t>719KB</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>31頁</t>
+          <t>25頁</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -10033,22 +10070,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
+          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>1,974KB</t>
+          <t>712KB</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>8頁</t>
+          <t>31頁</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／骨子案からの移植</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -10060,22 +10097,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
+          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>3,545KB</t>
+          <t>1,974KB</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>17頁</t>
+          <t>8頁</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
+          <t>令和8年法改正の反映／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -10087,22 +10124,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
+          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>249KB</t>
+          <t>3,545KB</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>8頁</t>
+          <t>17頁</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -10114,17 +10151,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>170KB</t>
+          <t>249KB</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>11頁</t>
+          <t>8頁</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -10141,22 +10178,22 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>141KB</t>
+          <t>170KB</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>7頁</t>
+          <t>11頁</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
@@ -10168,17 +10205,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>2KB</t>
+          <t>141KB</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>19行</t>
+          <t>7頁</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -10190,27 +10227,27 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>基本指針</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
+          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>265KB</t>
+          <t>2KB</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>19行</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>障がい児の論点（法改正）</t>
+          <t>高次脳機能障害者支援法</t>
         </is>
       </c>
     </row>
@@ -10222,17 +10259,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
+          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>273KB</t>
+          <t>265KB</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>9頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -10249,49 +10286,49 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
+          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>1,331KB</t>
+          <t>273KB</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>9頁</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
+          <t>障がい児の論点（法改正）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>村資料_自立支援協議会_20260525</t>
+          <t>基本指針</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>見込量と実績.pdf</t>
+          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>434KB</t>
+          <t>1,331KB</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
         </is>
       </c>
     </row>
@@ -10303,49 +10340,49 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>計画策定方針.pdf</t>
+          <t>見込量と実績.pdf</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>347KB</t>
+          <t>434KB</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>5頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／論点メモ</t>
+          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>村資料_自立支援協議会_20260525</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
+          <t>計画策定方針.pdf</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>417KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>3頁</t>
+          <t>5頁</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／論点メモ</t>
         </is>
       </c>
     </row>
@@ -10357,22 +10394,22 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>令和8年度住民向け成年後見講座.pdf</t>
+          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>803KB</t>
+          <t>417KB</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>3頁</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
@@ -10384,17 +10421,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>緊急連絡カード.pdf</t>
+          <t>令和8年度住民向け成年後見講座.pdf</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>828KB</t>
+          <t>803KB</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>1頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -10406,171 +10443,198 @@
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>現行計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+          <t>緊急連絡カード.pdf</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>1,582KB</t>
+          <t>828KB</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>1頁</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
+          <t>重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>県計画</t>
+          <t>現行計画</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>187KB</t>
+          <t>1,582KB</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>1141行</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
+          <t>県計画</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>187KB</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>1141行</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>村ホームページ3分野の棚卸し</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>関連計画</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>北塩原村_第10期介護保険事業計画_素案_e591fe8.md</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>422KB</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>3720行</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>エビデンスのファイルが生成器に現れない系統（4系統。なぜ現れないかを書く）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>なぜファイルが現れないか</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>第3回レビューへの対応</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>外部レビューの結果はチャットで受領したものであり、ファイルとして格納していない。指摘の全文は生成器の定数（REVIEW）に写してある</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>打合せ論点10項目</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>打合せ論点は口頭と当方の記録によるものであり、外部資料を直に開いていない</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr"/>
-      <c r="D54" s="9" t="inlineStr"/>
-      <c r="E54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr"/>
+      <c r="D55" s="9" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>関連法令3法</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>災害対策基本法・障害者雇用促進法・社会福祉士及び介護福祉士法の条文は生成器の定数に写してある（原典の入手はＳ-28等で依頼中）</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>図の元データは当方の算定（kitashiobara_common.py のPOPULATION・BENEFIT_YEARS 等）による</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr"/>
-      <c r="D56" s="9" t="inlineStr"/>
-      <c r="E56" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr"/>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A51:E51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_他メンバー版への対応履歴.xlsx
+++ b/output/北塩原村_他メンバー版への対応履歴.xlsx
@@ -9282,7 +9282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9295,7 +9295,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>生成器が実際に開いているエビデンス 45点</t>
+          <t>生成器が実際に開いているエビデンス 46点</t>
         </is>
       </c>
     </row>
@@ -9849,54 +9849,54 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>他メンバー素案_20261008</t>
+          <t>他AIレビュー_20261024_第3回</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
+          <t>RedTeam再レビュー報告書_第3版対応_R8.10.24.md</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>4,613KB</t>
+          <t>20KB</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>526段落</t>
+          <t>255行</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>他メンバー素案_20261008</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
+          <t>北塩原村_第8期障がい福祉計画_第4期障がい児福祉計画_素案_他メンバー版.docx</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>541KB</t>
+          <t>4,613KB</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>4頁</t>
+          <t>526段落</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>アンケートと見込量の整合／事実の誤りの書き換え（制度）／事実の誤りの書き換え（障がい児支援）／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／体系・工程の決定による書き換え／共生型サービスの適用可能性／前期計画のレッドチーム分析／国予算（令和7・8年度）／地域支援事業実施要綱／広域連携・圏域整合／情報公表制度と経営情報／意思決定支援ガイドライン第2版／指標の測定可能性／村ホームページ3分野の棚卸し／村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／村資料の点検／法定記載事項の点検／見込量算定のＲｅｄＴｅａｍ／計画の体系（案Ｃ）の反映／論点メモ／骨子案からの移植／高次脳機能障害者支援法／ＭＥＣＥ（利用の流れと報酬改定）／ＲｅｄＴｅａｍ（救急・防災・冬季）</t>
         </is>
       </c>
     </row>
@@ -9908,22 +9908,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
+          <t>介護保険最新情報Vol1404_令和7年度地域支援事業実施要綱等の改正点.pdf</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>2,628KB</t>
+          <t>541KB</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>38頁</t>
+          <t>4頁</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>国予算（令和7・8年度）</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -9935,17 +9935,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
+          <t>令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>257KB</t>
+          <t>2,628KB</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>38頁</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -9962,17 +9962,17 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
+          <t>令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>231KB</t>
+          <t>257KB</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>12頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -9989,22 +9989,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
+          <t>令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>669KB</t>
+          <t>231KB</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>74頁</t>
+          <t>12頁</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業実施要綱</t>
+          <t>国予算（令和7・8年度）</t>
         </is>
       </c>
     </row>
@@ -10016,22 +10016,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
+          <t>地域支援事業の実施について_老発0609001号_最終改正令和8年8月20日_001741386.pdf</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>347KB</t>
+          <t>669KB</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>22頁</t>
+          <t>74頁</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
+          <t>地域支援事業実施要綱</t>
         </is>
       </c>
     </row>
@@ -10043,22 +10043,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
+          <t>基幹相談支援センター一覧_令和7年4月1日時点_001698042.pdf</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>719KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>25頁</t>
+          <t>22頁</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版</t>
+          <t>事実の誤りの書き換え（障がい児支援）／広域連携・圏域整合</t>
         </is>
       </c>
     </row>
@@ -10070,17 +10070,17 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
+          <t>意思決定支援ガイドライン第2版_事例集_001749796.pdf</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>712KB</t>
+          <t>719KB</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>31頁</t>
+          <t>25頁</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -10097,22 +10097,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
+          <t>意思決定支援ガイドライン第2版_本文_001749795.pdf</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>1,974KB</t>
+          <t>712KB</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>8頁</t>
+          <t>31頁</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／骨子案からの移植</t>
+          <t>意思決定支援ガイドライン第2版</t>
         </is>
       </c>
     </row>
@@ -10124,22 +10124,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
+          <t>民法等の一部を改正する法律_令和8年法律第45号_001465481.pdf</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>3,545KB</t>
+          <t>1,974KB</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>17頁</t>
+          <t>8頁</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
+          <t>令和8年法改正の反映／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -10151,22 +10151,22 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
+          <t>社会福祉法等の一部を改正する法律の概要_令和8年法律第51号_001717214.pdf</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>249KB</t>
+          <t>3,545KB</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>8頁</t>
+          <t>17頁</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>情報公表制度と経営情報</t>
+          <t>令和8年法改正の反映／法定記載事項の点検／障がい児の論点（法改正）／骨子案からの移植</t>
         </is>
       </c>
     </row>
@@ -10178,17 +10178,17 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL1_001732679.pdf</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>170KB</t>
+          <t>249KB</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>11頁</t>
+          <t>8頁</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -10205,22 +10205,22 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
+          <t>障害福祉サービス等情報公表制度Q&amp;A_VOL2_001732680.pdf</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>141KB</t>
+          <t>170KB</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>7頁</t>
+          <t>11頁</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法</t>
+          <t>情報公表制度と経営情報</t>
         </is>
       </c>
     </row>
@@ -10232,17 +10232,17 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について_障精発0415第1号_001692858.pdf</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>2KB</t>
+          <t>141KB</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>19行</t>
+          <t>7頁</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -10254,27 +10254,27 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>基本指針</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
+          <t>高次脳機能障害者支援法施行令_令和8年政令第60号.txt</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>265KB</t>
+          <t>2KB</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>13頁</t>
+          <t>19行</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>障がい児の論点（法改正）</t>
+          <t>高次脳機能障害者支援法</t>
         </is>
       </c>
     </row>
@@ -10286,17 +10286,17 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
+          <t>基本指針改正_医療的ケア児支援法改正_障害児支援部会第21回_令和8年8月19日.pdf</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>273KB</t>
+          <t>265KB</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>9頁</t>
+          <t>13頁</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -10313,49 +10313,49 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
+          <t>基本指針改正_社会福祉法等改正_障害者部会第157回_令和8年7月10日.pdf</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>1,331KB</t>
+          <t>273KB</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>9頁</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
+          <t>障がい児の論点（法改正）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>村資料_自立支援協議会_20260525</t>
+          <t>基本指針</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>見込量と実績.pdf</t>
+          <t>第8期基本指針_告示本文_令和8年3月31日.pdf</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>434KB</t>
+          <t>1,331KB</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／村ホームページ3分野の棚卸し／法定記載事項の点検／第8次福島県医療計画との調和／第8次福島県医療計画との調和（表に行を足す）／見込量算定のＲｅｄＴｅａｍ</t>
         </is>
       </c>
     </row>
@@ -10367,49 +10367,49 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>計画策定方針.pdf</t>
+          <t>見込量と実績.pdf</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>347KB</t>
+          <t>434KB</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>5頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／論点メモ</t>
+          <t>村提供の給付の台帳による実績の表の書き換え／村提供の給付の台帳による評価の文の書き換え／村提供の給付の台帳の注記／論点メモ</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>村資料_高齢者施策_20261010</t>
+          <t>村資料_自立支援協議会_20260525</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
+          <t>計画策定方針.pdf</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>417KB</t>
+          <t>347KB</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>3頁</t>
+          <t>5頁</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
+          <t>他ＡＩのレビュー（見込量・ＫＰＩ）による書き換え／論点メモ</t>
         </is>
       </c>
     </row>
@@ -10421,22 +10421,22 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>令和8年度住民向け成年後見講座.pdf</t>
+          <t>令和8年度_北塩原村高齢者サービスの手引き.pdf</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>803KB</t>
+          <t>417KB</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>2頁</t>
+          <t>3頁</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>重点施策12件の評価設計</t>
+          <t>共生型サービスの適用可能性／村ホームページ3分野の棚卸し／重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
@@ -10448,17 +10448,17 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>緊急連絡カード.pdf</t>
+          <t>令和8年度住民向け成年後見講座.pdf</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>828KB</t>
+          <t>803KB</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>1頁</t>
+          <t>2頁</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -10470,170 +10470,197 @@
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>現行計画</t>
+          <t>村資料_高齢者施策_20261010</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
+          <t>緊急連絡カード.pdf</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>1,582KB</t>
+          <t>828KB</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>63頁</t>
+          <t>1頁</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
+          <t>重点施策12件の評価設計</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>県計画</t>
+          <t>現行計画</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+          <t>第4次障がい者計画_第7期障がい福祉計画_第3期障がい児福祉計画_本編.pdf</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>187KB</t>
+          <t>1,582KB</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>1141行</t>
+          <t>63頁</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>村ホームページ3分野の棚卸し</t>
+          <t>アンケート調査結果報告書のレビュー反映版の確認／事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合／前期計画のレッドチーム分析</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>県計画</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>第5次福島県障がい者計画_本文テキスト.txt</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>187KB</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>1141行</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>村ホームページ3分野の棚卸し</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
           <t>関連計画</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>北塩原村_第10期介護保険事業計画_素案_e591fe8.md</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>422KB</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>3720行</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>事実の誤りの書き換え（他計画との連携）／介護保険事業計画との整合</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>エビデンスのファイルが生成器に現れない系統（4系統。なぜ現れないかを書く）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>なぜファイルが現れないか</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr"/>
-      <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>第3回レビューへの対応</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>外部レビューの結果はチャットで受領したものであり、ファイルとして格納していない。指摘の全文は生成器の定数（REVIEW）に写してある</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>打合せ論点10項目</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>打合せ論点は口頭と当方の記録によるものであり、外部資料を直に開いていない</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr"/>
-      <c r="D55" s="9" t="inlineStr"/>
-      <c r="E55" s="9" t="inlineStr"/>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr"/>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>関連法令3法</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>災害対策基本法・障害者雇用促進法・社会福祉士及び介護福祉士法の条文は生成器の定数に写してある（原典の入手はＳ-28等で依頼中）</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>当方が作った図</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>図の元データは当方の算定（kitashiobara_common.py のPOPULATION・BENEFIT_YEARS 等）による</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr"/>
+      <c r="C58" s="9" t="inlineStr"/>
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
